--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -438,6 +438,156 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2438400" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1200150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1895475" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1847850" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2247900" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -730,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -779,7 +929,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Lâm Đồng, ngày 09 tháng 09 năm 2026</t>
+          <t>Lâm Đồng, ngày 14 tháng 09 năm 2026</t>
         </is>
       </c>
     </row>
@@ -826,14 +976,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tổng số: 112 mục (Đã chốt: 15 mục)</t>
+          <t>Tổng số: 112 mục (Đã chốt: 46 mục)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 32.385.281.416 đ</t>
+          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 31.370.614.666 đ</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -841,7 +991,7 @@
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>TIẾT KIỆM CHO NHÀ MÁY: -5.937.874.584 đ  (15.57%)</t>
+          <t>TIẾT KIỆM CHO NHÀ MÁY: -1.292.573.334 đ  (3.39%)</t>
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
@@ -1586,23 +1736,22 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>3.96.13.320.USA.00.000</t>
+          <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-NSX: MERRICK</t>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Merrick/ Mỹ</t>
+          <t>Swagelok/ Đức</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1614,16 +1763,16 @@
         <v>2</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>56105000</v>
+        <v>19000000</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>23000000</v>
+        <v>12350000</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>46000000</v>
+        <v>24700000</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>66210000</v>
+        <v>13300000</v>
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
@@ -1637,32 +1786,22 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Chưa có mã vật tư</t>
+          <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Lining Plate (Compound Armour Plate)
-Tấm lót thân máy nghiền
-Bao gồm 106 chi tiết (tấm)
-Chế tạo bằng thép Kalmetall W100/Kalenborn
-- Vật liệu: Thép 2 thành phần Kalmetall W100 - Kalenborn
-- Độ dày: 16mm ( 8+8 )
-- Độ dày: 10mm ( 6+4 )
-- Thép nền S235JRG2
-- Lớp phủ hợp kim Chromium Carbides: %C~5; %Cr~30; %Fe + others Balance 
-- Độ cứng ~ 700HV trên toàn bộ lớp phủ
-- Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>ML/ Ba Lan</t>
+          <t>Swagelok/ Đức</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -1674,16 +1813,16 @@
         <v>2</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>2618304000</v>
+        <v>1700000</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>1300000</v>
+        <v>1319000</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>2600000</v>
+        <v>2638000</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>5234008000</v>
+        <v>762000</v>
       </c>
       <c r="L26" s="19" t="inlineStr">
         <is>
@@ -1697,15 +1836,1305 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
+          <t>4.82.22.025.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>644760</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>64476000</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>195524000</v>
+      </c>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner:
+- Model: TZIDC-V18345- 2020521001
+-Type: Double acting 
+-Sofw.Rev: 3 
+-Supply press: 1,4 ~ 6 bar 
+-Input: Analog 4 ~ 20 mA
+ -Loss of electric: Fail freeze
+- Option: Analog feedback, FSK, Position indicator 
+-NSX: ABB</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>83484000</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>417420000</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
+- NSX: MINCO 
+- Element: Platinum 
+- Element length: 6.4 mm 
+- Cable dimension "C": 1778 mm 
+- Cable dimension "L": 8890 mm 
+- Single duplex: Duplex 
+- Sheath: 2.9 mm OD 
+- Type: RTD PT100, 3 Wire 
+- Range: 0 - 260 °C</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Minco/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>2076555</v>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
+Range: 0.5m to 15m Signal: 4 - 20 mA 
+Supply power: 115 to 230 V AC or 24 V DC.
+NSX: ABB</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>113235859</v>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+Model: MA3145-230-2-R
+- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
+- Điện áp định mức (Voltage rating): 230 VAC.
+- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
+NSX: Cooper Crouse-Hinds MTL / Eaton</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Eaton/ Slovenia</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>21609600</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>64828800</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>40171200</v>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>3.34.40.009.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)
+Model: WP/FS-25VFL
+Switch : SPDT Snap Acting Micro
+Rating : 5A 250VAC 
+NSX: Dag Process Instruments Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="L32" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+- Model: PR30-10AC
+Đường kính cạnh phát hiện: 30mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NC
+- Protection: IP67</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>1219000</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>911127</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>1822254</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>615746</v>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+- Model: PR18-8AO
+- Đường kính đầu dò: 18mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NO
+- Protection: IP67</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>577200</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>577200</v>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>572800</v>
+      </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>420000</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>420000</v>
+      </c>
+      <c r="K35" s="18" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+- Material: PVC
+- Maker: Eunchang T&amp;C</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>235</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>66000</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>26000</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>6110000</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+- Maker: Eunchang T&amp;C</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>68000</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>672000</v>
+      </c>
+      <c r="K37" s="18" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Length: 3m / cây
+- Material: Copper
+- Maker: EunchangT&amp;C</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Cây</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>909000</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>890000</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>532000</v>
+      </c>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.133.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913
+Control station composition: 06 push buttons + 01 emergency stop
+Product compatibility: 
+ZB2BE102 for emergency stop, XEN-G1191 for each direction
+Color: Yellow</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>13319000</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="K39" s="18" t="n">
+        <v>10028600</v>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>MT/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>610000</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>314600</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>314600</v>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>295400</v>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>37000</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="K41" s="18" t="n">
+        <v>780000</v>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm.
+Vật liệu: Inox 304</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>2254000</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>578078</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>1156156</v>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>3351844</v>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+Điện áp: 450/750V
+Cách điện: PVC, dẻo
+NSX: Imatek</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Imatek/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>711000</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>76000</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>31750000</v>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>770000</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>330000</v>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+Control station composition: 06, push buttons + 01 emergency stop</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>7406000</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>4095815</v>
+      </c>
+      <c r="L46" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn:
+ + Kích thước: 60 x 175x 3mm
+ + Vật liệu: thép</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>656000</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>585000</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>585000</v>
+      </c>
+      <c r="K47" s="18" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPN
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>21120000</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>19360000</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>580800000</v>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>5.01.07.302.FRA.00.000</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>SKF/ Pháp</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>158000</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>85000</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>170000</v>
+      </c>
+      <c r="K49" s="18" t="n">
+        <v>146000</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
++ Cycloidal Gear Reducer Type: 
+XLD3-59-1.1KW</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
++ Cycloidal Gear Reducer Type: 
+XLD3-59-1.1KW
++ Input Power: 1.1 KW
++ Transmission Ratio: 59
++ Nhà sản xuất: JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>58240000</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
@@ -1722,90 +3151,448 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>Grundfos/ Eu</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G51" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="H51" s="17" t="n">
         <v>770000000</v>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="I51" s="17" t="n">
         <v>750000000</v>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J51" s="17" t="n">
         <v>1500000000</v>
       </c>
-      <c r="K27" s="18" t="n">
+      <c r="K51" s="18" t="n">
         <v>40000000</v>
       </c>
-      <c r="L27" s="19" t="inlineStr">
+      <c r="L51" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>4.31.28.586.JPN.99.000</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>Kiswel/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>725000</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>124956</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>9996480</v>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>48003520</v>
+      </c>
+      <c r="L52" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>5.33.85.051.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Phanh đuôi động cơ, model: BFK458-18E</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Model: BFK458-18E
+Size: 18
+Đường kính phủ bì: 218,6mm
+Lỗ lắp bulong: 6xM8
+Đường kính vòng chia bulong: 196mm
+Điện áp: 205VDC
+Nhà sản xuất: INTORQ</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>Intorq/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>63063000</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>65366000</v>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>3.84.64.021.GER.00.000</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>- Model:169800
+- Điện áp vào: 220-440VAC
+Điện áp ra: 110-205VDC</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Siemens/ Đức</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>210600</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>210600</v>
+      </c>
+      <c r="K54" s="18" t="n">
+        <v>2189400</v>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>1.31.23.425.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>Shell/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>560000</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>265980</v>
+      </c>
+      <c r="J55" s="17" t="n">
+        <v>5319600</v>
+      </c>
+      <c r="K55" s="18" t="n">
+        <v>5880400</v>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>4.88.65.314.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>904000</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>904000</v>
+      </c>
+      <c r="K56" s="18" t="n">
+        <v>5796000</v>
+      </c>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>5.04.01.308.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>30294</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>60588</v>
+      </c>
+      <c r="K57" s="18" t="n">
+        <v>14539412</v>
+      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>4.88.67.084.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>1895400</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>3790800</v>
+      </c>
+      <c r="K58" s="18" t="n">
+        <v>12009200</v>
+      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>TỔNG CỘNG CÁC MỤC ĐÃ CHỐT THẨM ĐỊNH:</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="22" t="n">
-        <v>2953039416.5</v>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v>5937874583.5</v>
-      </c>
-      <c r="L28" s="21" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="22" t="n">
+        <v>4382839665.5</v>
+      </c>
+      <c r="K59" s="23" t="n">
+        <v>1292573334.5</v>
+      </c>
+      <c r="L59" s="21" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="24" t="inlineStr">
         <is>
           <t>NGƯỜI LẬP BÁO CÁO / THƯ KÝ TỔ TTĐ</t>
         </is>
       </c>
-      <c r="J31" s="24" t="inlineStr">
+      <c r="J62" s="24" t="inlineStr">
         <is>
           <t>TỔ TRƯỞNG TỔ THẨM ĐỊNH DỰ TOÁN</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="25" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
-      <c r="J32" s="25" t="inlineStr">
+      <c r="J63" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>Nguyễn Anh Hiếu</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr">
+      <c r="J68" s="26" t="inlineStr">
         <is>
           <t>...................................................</t>
         </is>
@@ -1813,19 +3600,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:G9"/>
     <mergeCell ref="H9:L9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A5:L5"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A59:I59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId1"/>
@@ -1843,6 +3630,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1883,7 +3701,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 09/09/2026 09:12</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 14/09/2026 21:31</t>
         </is>
       </c>
     </row>
@@ -3167,176 +4985,176 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="31" t="n">
         <v>19000000</v>
       </c>
-      <c r="I24" s="17" t="n">
+      <c r="I24" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>2.46.35.019.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J24" s="31" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="K24" s="31" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="L24" s="23" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N24" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="31" t="n">
         <v>1700000</v>
       </c>
-      <c r="I25" s="17" t="n">
+      <c r="I25" s="31" t="n">
         <v>3400000</v>
       </c>
-      <c r="J25" s="17" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>4.82.22.013.USA.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J25" s="31" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="K25" s="31" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <v>762000</v>
+      </c>
+      <c r="M25" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N25" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>4.82.22.025.CHN.00.000</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H26" s="31" t="n">
         <v>2600000</v>
       </c>
-      <c r="I26" s="17" t="n">
+      <c r="I26" s="31" t="n">
         <v>260000000</v>
       </c>
-      <c r="J26" s="17" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v>260000000</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>4.82.22.025.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J26" s="31" t="n">
+        <v>644760</v>
+      </c>
+      <c r="K26" s="31" t="n">
+        <v>64476000</v>
+      </c>
+      <c r="L26" s="23" t="n">
+        <v>195524000</v>
+      </c>
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N26" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -3399,20 +5217,20 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>5.33.70.184.GER.99.000</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner:
 - Model: TZIDC-V18345- 2020521001
@@ -3425,60 +5243,60 @@
 -NSX: ABB</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="31" t="n">
         <v>85000000</v>
       </c>
-      <c r="I28" s="17" t="n">
+      <c r="I28" s="31" t="n">
         <v>425000000</v>
       </c>
-      <c r="J28" s="17" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="K28" s="17" t="n">
-        <v>425000000</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>5.33.70.184.GER.99.000 | Thay thế các bộ positioner điều khiển damper gió SA bị xì khí nén của tổ máy S2 | Vật tư được đề xuất trong KHSXKD năm 2026,nhưng phát sinh hư hỏng thêm 2 bộ vượt nhu cầu dự kiến, nên đề xuất mua sắm bổ sung. Tên vật tư được đặt lại theo quy tắc chuẩn hóa.</t>
+      <c r="J28" s="31" t="n">
+        <v>83484000</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>417420000</v>
+      </c>
+      <c r="L28" s="23" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N28" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>3.96.13.144.USA.00.000</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
 - NSX: MINCO 
@@ -3492,119 +5310,119 @@
 - Range: 0 - 260 °C</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Minco/ Mỹ</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H29" s="31" t="n">
         <v>30000000</v>
       </c>
-      <c r="I29" s="17" t="n">
+      <c r="I29" s="31" t="n">
         <v>30000000</v>
       </c>
-      <c r="J29" s="17" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.144.USA.00.000 | BBKT- 1008/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến nhiệt độ số 2 gối chặn BFPT B S2 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH TXBS.26.562). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="J29" s="31" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="K29" s="31" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="L29" s="23" t="n">
+        <v>2076555</v>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N29" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Merrick/ Mỹ</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G30" s="31" t="n">
+      <c r="G30" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="H30" s="17" t="n">
         <v>56105000</v>
       </c>
-      <c r="I30" s="31" t="n">
+      <c r="I30" s="17" t="n">
         <v>112210000</v>
       </c>
-      <c r="J30" s="31" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="K30" s="31" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <v>66210000</v>
-      </c>
-      <c r="M30" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N30" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J30" s="17" t="n">
+        <v>56105000</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>112210000</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>3.96.13.320.USA.00.000 | BBKT- 1033/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến khối lượng than – máy cấp A tổ máy S3 báo sai giá trị.Vật tư không có trong KH SXKD 2026. | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
 Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
@@ -3613,42 +5431,42 @@
 NSX: ABB</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="H31" s="31" t="n">
         <v>189000000</v>
       </c>
-      <c r="I31" s="17" t="n">
+      <c r="I31" s="31" t="n">
         <v>189000000</v>
       </c>
-      <c r="J31" s="17" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="K31" s="17" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 955/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến báo mức nước tổng kênh tuần hoàn tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J31" s="31" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="K31" s="31" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <v>113235859</v>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N31" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4444,20 +6262,20 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="14" t="n">
+      <c r="A45" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="30" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
 Model: MA3145-230-2-R
@@ -4467,42 +6285,42 @@
 NSX: Cooper Crouse-Hinds MTL / Eaton</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>Eaton/ Slovenia</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G45" s="17" t="n">
+      <c r="G45" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="17" t="n">
+      <c r="H45" s="31" t="n">
         <v>35000000</v>
       </c>
-      <c r="I45" s="17" t="n">
+      <c r="I45" s="31" t="n">
         <v>105000000</v>
       </c>
-      <c r="J45" s="17" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="K45" s="17" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="L45" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N45" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1089/2026/VH-VT4_ Kiểm tra, khắc phục các con đo lưu lượng nước biển S3 không. hiển thị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J45" s="31" t="n">
+        <v>21609600</v>
+      </c>
+      <c r="K45" s="31" t="n">
+        <v>64828800</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <v>40171200</v>
+      </c>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N45" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4567,20 +6385,20 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>3.34.40.009.IND.00.000</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="30" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)
 Model: WP/FS-25VFL
@@ -4589,42 +6407,42 @@
 NSX: Dag Process Instruments Pvt. Ltd</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G47" s="17" t="n">
+      <c r="G47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="17" t="n">
+      <c r="H47" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="I47" s="17" t="n">
+      <c r="I47" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="J47" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="K47" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="L47" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N47" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1122/2026/VH-VT4_ Kiểm tra, lỗi tín hiệu lưu lượng gió chèn 1B – ESP -  S1 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J47" s="31" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="K47" s="31" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N47" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4692,20 +6510,20 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="14" t="n">
+      <c r="A49" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>3.96.13.165.KOR.00.000</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR30-10AC
@@ -4715,60 +6533,60 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" s="29" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="17" t="n">
+      <c r="H49" s="31" t="n">
         <v>1219000</v>
       </c>
-      <c r="I49" s="17" t="n">
+      <c r="I49" s="31" t="n">
         <v>2438000</v>
       </c>
-      <c r="J49" s="17" t="n">
-        <v>1219000</v>
-      </c>
-      <c r="K49" s="17" t="n">
-        <v>2438000</v>
-      </c>
-      <c r="L49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.165.KOR.00.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương, kích thước theo file BBKT đính kèm</t>
+      <c r="J49" s="31" t="n">
+        <v>911127</v>
+      </c>
+      <c r="K49" s="31" t="n">
+        <v>1822254</v>
+      </c>
+      <c r="L49" s="23" t="n">
+        <v>615746</v>
+      </c>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N49" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="28" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>3.96.13.114.KOR.99.000</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR18-8AO
@@ -4778,42 +6596,42 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" s="29" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="17" t="n">
+      <c r="H50" s="31" t="n">
         <v>1150000</v>
       </c>
-      <c r="I50" s="17" t="n">
+      <c r="I50" s="31" t="n">
         <v>1150000</v>
       </c>
-      <c r="J50" s="17" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="K50" s="17" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="L50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N50" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.114.KOR.99.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J50" s="31" t="n">
+        <v>577200</v>
+      </c>
+      <c r="K50" s="31" t="n">
+        <v>577200</v>
+      </c>
+      <c r="L50" s="23" t="n">
+        <v>572800</v>
+      </c>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N50" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4859,10 +6677,10 @@
         <v>597060000</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>535000</v>
+        <v>465000</v>
       </c>
       <c r="K51" s="17" t="n">
-        <v>686940000</v>
+        <v>597060000</v>
       </c>
       <c r="L51" s="17" t="n">
         <v>0</v>
@@ -4879,62 +6697,62 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>3.34.20.134.CHN.00.000</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G52" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="17" t="n">
+      <c r="H52" s="31" t="n">
         <v>5784000</v>
       </c>
-      <c r="I52" s="17" t="n">
+      <c r="I52" s="31" t="n">
         <v>5784000</v>
       </c>
-      <c r="J52" s="17" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="K52" s="17" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="L52" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>3.34.20.134.CHN.00.000 | Sửa chữa tời điện Tời điện số 15 tấn B Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J52" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="K52" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L52" s="23" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="M52" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N52" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5001,139 +6819,139 @@
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="14" t="n">
+      <c r="A54" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>4.90.80.030.KOR.00.000</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
 - Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E54" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G54" s="17" t="n">
+      <c r="G54" s="31" t="n">
         <v>235</v>
       </c>
-      <c r="H54" s="17" t="n">
+      <c r="H54" s="31" t="n">
         <v>66000</v>
       </c>
-      <c r="I54" s="17" t="n">
+      <c r="I54" s="31" t="n">
         <v>15510000</v>
       </c>
-      <c r="J54" s="17" t="n">
-        <v>66000</v>
-      </c>
-      <c r="K54" s="17" t="n">
-        <v>15510000</v>
-      </c>
-      <c r="L54" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N54" s="16" t="inlineStr">
-        <is>
-          <t>4.90.80.030.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J54" s="31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K54" s="31" t="n">
+        <v>6110000</v>
+      </c>
+      <c r="L54" s="23" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N54" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>4.90.80.027.KOR.00.000</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F55" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n">
+      <c r="G55" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="H55" s="17" t="n">
+      <c r="H55" s="31" t="n">
         <v>68000</v>
       </c>
-      <c r="I55" s="17" t="n">
+      <c r="I55" s="31" t="n">
         <v>2176000</v>
       </c>
-      <c r="J55" s="17" t="n">
-        <v>68000</v>
-      </c>
-      <c r="K55" s="17" t="n">
-        <v>2176000</v>
-      </c>
-      <c r="L55" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N55" s="16" t="inlineStr">
-        <is>
-          <t>4.90.80.027.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J55" s="31" t="n">
+        <v>21000</v>
+      </c>
+      <c r="K55" s="31" t="n">
+        <v>672000</v>
+      </c>
+      <c r="L55" s="23" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N55" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="14" t="n">
+      <c r="A56" s="28" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>2.08.37.001.KOR.97.000</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn)</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn):
 - Iđm: 60A;
@@ -5143,42 +6961,42 @@
 - Maker: EunchangT&amp;C</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr">
+      <c r="E56" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F56" s="28" t="inlineStr">
         <is>
           <t>Cây</t>
         </is>
       </c>
-      <c r="G56" s="17" t="n">
+      <c r="G56" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="H56" s="17" t="n">
+      <c r="H56" s="31" t="n">
         <v>909000</v>
       </c>
-      <c r="I56" s="17" t="n">
+      <c r="I56" s="31" t="n">
         <v>25452000</v>
       </c>
-      <c r="J56" s="17" t="n">
-        <v>909000</v>
-      </c>
-      <c r="K56" s="17" t="n">
-        <v>25452000</v>
-      </c>
-      <c r="L56" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>2.08.37.001.KOR.97.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J56" s="31" t="n">
+        <v>890000</v>
+      </c>
+      <c r="K56" s="31" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="L56" s="23" t="n">
+        <v>532000</v>
+      </c>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N56" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5303,21 +7121,21 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="14" t="n">
+      <c r="A59" s="28" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>3.34.20.133.CHN.99.000</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913
@@ -5327,101 +7145,101 @@
 Color: Yellow</t>
         </is>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F59" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G59" s="17" t="n">
+      <c r="G59" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="17" t="n">
+      <c r="H59" s="31" t="n">
         <v>13319000</v>
       </c>
-      <c r="I59" s="17" t="n">
+      <c r="I59" s="31" t="n">
         <v>13319000</v>
       </c>
-      <c r="J59" s="17" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="K59" s="17" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="L59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 10 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J59" s="31" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="K59" s="31" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="L59" s="23" t="n">
+        <v>10028600</v>
+      </c>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N59" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="14" t="n">
+      <c r="A60" s="28" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn
 Kích thước: rộng 25mm x dài 60mm</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E60" s="29" t="inlineStr">
         <is>
           <t>MT/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F60" s="14" t="inlineStr">
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G60" s="17" t="n">
+      <c r="G60" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="17" t="n">
+      <c r="H60" s="31" t="n">
         <v>610000</v>
       </c>
-      <c r="I60" s="17" t="n">
+      <c r="I60" s="31" t="n">
         <v>610000</v>
       </c>
-      <c r="J60" s="17" t="n">
-        <v>610000</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>610000</v>
-      </c>
-      <c r="L60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J60" s="31" t="n">
+        <v>314600</v>
+      </c>
+      <c r="K60" s="31" t="n">
+        <v>314600</v>
+      </c>
+      <c r="L60" s="23" t="n">
+        <v>295400</v>
+      </c>
+      <c r="M60" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N60" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5543,121 +7361,121 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="14" t="n">
+      <c r="A63" s="28" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>2.50.05.003.CHN.00.000</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="30" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="F63" s="28" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G63" s="17" t="n">
+      <c r="G63" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="H63" s="17" t="n">
+      <c r="H63" s="31" t="n">
         <v>37000</v>
       </c>
-      <c r="I63" s="17" t="n">
+      <c r="I63" s="31" t="n">
         <v>2220000</v>
       </c>
-      <c r="J63" s="17" t="n">
-        <v>37000</v>
-      </c>
-      <c r="K63" s="17" t="n">
-        <v>2220000</v>
-      </c>
-      <c r="L63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>2.50.05.003.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J63" s="31" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="L63" s="23" t="n">
+        <v>780000</v>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N63" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="14" t="n">
+      <c r="A64" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm.
 Vật liệu: Inox 304</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
+      <c r="E64" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F64" s="14" t="inlineStr">
+      <c r="F64" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G64" s="17" t="n">
+      <c r="G64" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="17" t="n">
+      <c r="H64" s="31" t="n">
         <v>56000</v>
       </c>
-      <c r="I64" s="17" t="n">
+      <c r="I64" s="31" t="n">
         <v>56000</v>
       </c>
-      <c r="J64" s="17" t="n">
-        <v>56000</v>
-      </c>
-      <c r="K64" s="17" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J64" s="31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L64" s="23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N64" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5978,22 +7796,22 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="14" t="n">
+      <c r="A70" s="28" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>2.06.60.080.TPE.00.000</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
 Size: 80x51x3mm</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
@@ -6002,42 +7820,42 @@
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>ITS/ Đài Loan</t>
         </is>
       </c>
-      <c r="F70" s="14" t="inlineStr">
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G70" s="17" t="n">
+      <c r="G70" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="17" t="n">
+      <c r="H70" s="31" t="n">
         <v>2254000</v>
       </c>
-      <c r="I70" s="17" t="n">
+      <c r="I70" s="31" t="n">
         <v>4508000</v>
       </c>
-      <c r="J70" s="17" t="n">
-        <v>2254000</v>
-      </c>
-      <c r="K70" s="17" t="n">
-        <v>4508000</v>
-      </c>
-      <c r="L70" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N70" s="16" t="inlineStr">
-        <is>
-          <t>2.06.60.080.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J70" s="31" t="n">
+        <v>578078</v>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>1156156</v>
+      </c>
+      <c r="L70" s="23" t="n">
+        <v>3351844</v>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N70" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6104,22 +7922,22 @@
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="14" t="n">
+      <c r="A72" s="28" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>3.15.44.076.CHN.00.000</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
 Ruột mềm</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
@@ -6129,223 +7947,223 @@
 NSX: Imatek</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>Imatek/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F72" s="14" t="inlineStr">
+      <c r="F72" s="28" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G72" s="17" t="n">
+      <c r="G72" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="H72" s="17" t="n">
+      <c r="H72" s="31" t="n">
         <v>711000</v>
       </c>
-      <c r="I72" s="17" t="n">
+      <c r="I72" s="31" t="n">
         <v>35550000</v>
       </c>
-      <c r="J72" s="17" t="n">
-        <v>711000</v>
-      </c>
-      <c r="K72" s="17" t="n">
-        <v>35550000</v>
-      </c>
-      <c r="L72" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N72" s="16" t="inlineStr">
-        <is>
-          <t>3.15.44.076.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J72" s="31" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="L72" s="23" t="n">
+        <v>31750000</v>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N72" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="14" t="n">
+      <c r="A73" s="28" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>3.20.22.003.TPE.00.000</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" s="30" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="30" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="F73" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G73" s="17" t="n">
+      <c r="G73" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="H73" s="17" t="n">
+      <c r="H73" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="I73" s="17" t="n">
+      <c r="I73" s="31" t="n">
         <v>1100000</v>
       </c>
-      <c r="J73" s="17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K73" s="17" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L73" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N73" s="16" t="inlineStr">
-        <is>
-          <t>3.20.22.003.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J73" s="31" t="n">
+        <v>14000</v>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>770000</v>
+      </c>
+      <c r="L73" s="23" t="n">
+        <v>330000</v>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N73" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="14" t="n">
+      <c r="A74" s="28" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>3.34.20.130.CHN.99.000</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713
 Control station composition: 06, push buttons + 01 emergency stop</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E74" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F74" s="14" t="inlineStr">
+      <c r="F74" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="17" t="n">
+      <c r="H74" s="31" t="n">
         <v>7406000</v>
       </c>
-      <c r="I74" s="17" t="n">
+      <c r="I74" s="31" t="n">
         <v>7406000</v>
       </c>
-      <c r="J74" s="17" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="K74" s="17" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="L74" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>3.34.20.130.CHN.99.000 | Sửa chữa Tời điện Tời điện 3 tấn máy nén khí turbine theo BBKT 624/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J74" s="31" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="L74" s="23" t="n">
+        <v>4095815</v>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N74" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="14" t="n">
+      <c r="A75" s="28" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C75" s="16" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn:
  + Kích thước: 60 x 175x 3mm
  + Vật liệu: thép</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="F75" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="31" t="n">
         <v>656000</v>
       </c>
-      <c r="I75" s="17" t="n">
+      <c r="I75" s="31" t="n">
         <v>656000</v>
       </c>
-      <c r="J75" s="17" t="n">
-        <v>656000</v>
-      </c>
-      <c r="K75" s="17" t="n">
-        <v>656000</v>
-      </c>
-      <c r="L75" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N75" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J75" s="31" t="n">
+        <v>585000</v>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>585000</v>
+      </c>
+      <c r="L75" s="23" t="n">
+        <v>71000</v>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N75" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6388,10 +8206,10 @@
         <v>12500000</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>625000</v>
+        <v>0</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="L76" s="17" t="n">
         <v>0</v>
@@ -6408,20 +8226,20 @@
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="14" t="n">
+      <c r="A77" s="28" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>3.82.63.103.LTU.00.000</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO HBS 01 - FPN</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO:
 - Hãng: ABB
@@ -6429,42 +8247,42 @@
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>ABB/ Lithuania</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="F77" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G77" s="17" t="n">
+      <c r="G77" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="H77" s="17" t="n">
+      <c r="H77" s="31" t="n">
         <v>21120000</v>
       </c>
-      <c r="I77" s="17" t="n">
+      <c r="I77" s="31" t="n">
         <v>633600000</v>
       </c>
-      <c r="J77" s="17" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="K77" s="17" t="n">
-        <v>633600000</v>
-      </c>
-      <c r="L77" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N77" s="16" t="inlineStr">
-        <is>
-          <t>3.82.63.103.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung  | Vật tư không có trong KHSXKD 2026</t>
+      <c r="J77" s="31" t="n">
+        <v>19360000</v>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>580800000</v>
+      </c>
+      <c r="L77" s="23" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N77" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6510,10 +8328,10 @@
         <v>549120000</v>
       </c>
       <c r="J78" s="17" t="n">
-        <v>21120000</v>
+        <v>0</v>
       </c>
       <c r="K78" s="17" t="n">
-        <v>549120000</v>
+        <v>0</v>
       </c>
       <c r="L78" s="17" t="n">
         <v>0</v>
@@ -6571,10 +8389,10 @@
         <v>183500000</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>21120000</v>
+        <v>18350000</v>
       </c>
       <c r="K79" s="17" t="n">
-        <v>211200000</v>
+        <v>183500000</v>
       </c>
       <c r="L79" s="17" t="n">
         <v>0</v>
@@ -6649,60 +8467,60 @@
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="14" t="n">
+      <c r="A81" s="28" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>5.01.07.302.FRA.00.000</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="30" t="inlineStr">
         <is>
           <t>Bạc đạn 6302</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="30" t="inlineStr">
         <is>
           <t>Bạc đạn 6302</t>
         </is>
       </c>
-      <c r="E81" s="15" t="inlineStr">
+      <c r="E81" s="29" t="inlineStr">
         <is>
           <t>SKF/ Pháp</t>
         </is>
       </c>
-      <c r="F81" s="14" t="inlineStr">
+      <c r="F81" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G81" s="17" t="n">
+      <c r="G81" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H81" s="17" t="n">
+      <c r="H81" s="31" t="n">
         <v>158000</v>
       </c>
-      <c r="I81" s="17" t="n">
+      <c r="I81" s="31" t="n">
         <v>316000</v>
       </c>
-      <c r="J81" s="17" t="n">
-        <v>158000</v>
-      </c>
-      <c r="K81" s="17" t="n">
-        <v>316000</v>
-      </c>
-      <c r="L81" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N81" s="16" t="inlineStr">
-        <is>
-          <t>5.01.07.302.FRA.00.000 | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J81" s="31" t="n">
+        <v>85000</v>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>170000</v>
+      </c>
+      <c r="L81" s="23" t="n">
+        <v>146000</v>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N81" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6745,10 +8563,10 @@
         <v>1776000</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>444000</v>
+        <v>0</v>
       </c>
       <c r="K82" s="17" t="n">
-        <v>1776000</v>
+        <v>0</v>
       </c>
       <c r="L82" s="17" t="n">
         <v>0</v>
@@ -6765,22 +8583,22 @@
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="14" t="n">
+      <c r="A83" s="28" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="30" t="inlineStr">
         <is>
           <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
 XLD3-59-1.1KW</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="30" t="inlineStr">
         <is>
           <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
@@ -6790,42 +8608,42 @@
 + Nhà sản xuất: JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="E83" s="29" t="inlineStr">
         <is>
           <t>JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F83" s="14" t="inlineStr">
+      <c r="F83" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G83" s="17" t="n">
+      <c r="G83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="17" t="n">
+      <c r="H83" s="31" t="n">
         <v>58240000</v>
       </c>
-      <c r="I83" s="17" t="n">
+      <c r="I83" s="31" t="n">
         <v>58240000</v>
       </c>
-      <c r="J83" s="17" t="n">
-        <v>58240000</v>
-      </c>
-      <c r="K83" s="17" t="n">
-        <v>58240000</v>
-      </c>
-      <c r="L83" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J83" s="31" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="K83" s="31" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="L83" s="23" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N83" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6937,10 +8755,10 @@
         <v>1476992000</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>738496000</v>
+        <v>0</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>1476992000</v>
+        <v>0</v>
       </c>
       <c r="L85" s="17" t="n">
         <v>0</v>
@@ -6957,20 +8775,20 @@
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="28" t="n">
+      <c r="A86" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C86" s="30" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
         </is>
       </c>
-      <c r="D86" s="30" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
@@ -6985,42 +8803,42 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E86" s="29" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr">
         <is>
           <t>ML/ Ba Lan</t>
         </is>
       </c>
-      <c r="F86" s="28" t="inlineStr">
+      <c r="F86" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G86" s="31" t="n">
+      <c r="G86" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="31" t="n">
+      <c r="H86" s="17" t="n">
         <v>2618304000</v>
       </c>
-      <c r="I86" s="31" t="n">
+      <c r="I86" s="17" t="n">
         <v>5236608000</v>
       </c>
-      <c r="J86" s="31" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="K86" s="31" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="L86" s="23" t="n">
-        <v>5234008000</v>
-      </c>
-      <c r="M86" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N86" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J86" s="17" t="n">
+        <v>2618304000</v>
+      </c>
+      <c r="K86" s="17" t="n">
+        <v>5236608000</v>
+      </c>
+      <c r="L86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế mới tấm lining ở vách thùng nghiền, phía sau con lăn, cửa manhole các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -7065,10 +8883,10 @@
         <v>326400000</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>16320000</v>
+        <v>0</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>326400000</v>
+        <v>0</v>
       </c>
       <c r="L87" s="17" t="n">
         <v>0</v>
@@ -7181,10 +8999,10 @@
         <v>1587600000</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>264600000</v>
+        <v>0</v>
       </c>
       <c r="K89" s="17" t="n">
-        <v>1587600000</v>
+        <v>0</v>
       </c>
       <c r="L89" s="17" t="n">
         <v>0</v>
@@ -7834,10 +9652,10 @@
         <v>676000000</v>
       </c>
       <c r="J100" s="17" t="n">
-        <v>368000000</v>
+        <v>338000000</v>
       </c>
       <c r="K100" s="17" t="n">
-        <v>736000000</v>
+        <v>676000000</v>
       </c>
       <c r="L100" s="17" t="n">
         <v>0</v>
@@ -8098,60 +9916,60 @@
       </c>
     </row>
     <row r="105" ht="24" customHeight="1">
-      <c r="A105" s="14" t="n">
+      <c r="A105" s="28" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B105" s="29" t="inlineStr">
         <is>
           <t>4.31.28.586.JPN.99.000</t>
         </is>
       </c>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="C105" s="30" t="inlineStr">
         <is>
           <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
+      <c r="D105" s="30" t="inlineStr">
         <is>
           <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương</t>
         </is>
       </c>
-      <c r="E105" s="15" t="inlineStr">
+      <c r="E105" s="29" t="inlineStr">
         <is>
           <t>Kiswel/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F105" s="14" t="inlineStr">
+      <c r="F105" s="28" t="inlineStr">
         <is>
           <t>Kg</t>
         </is>
       </c>
-      <c r="G105" s="17" t="n">
+      <c r="G105" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="H105" s="17" t="n">
+      <c r="H105" s="31" t="n">
         <v>725000</v>
       </c>
-      <c r="I105" s="17" t="n">
+      <c r="I105" s="31" t="n">
         <v>58000000</v>
       </c>
-      <c r="J105" s="17" t="n">
-        <v>725000</v>
-      </c>
-      <c r="K105" s="17" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="L105" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N105" s="16" t="inlineStr">
-        <is>
-          <t>4.31.28.586.JPN.99.000 | Vật tư dùng để hàn thanh gia cường tầng cánh IP 18/20 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+      <c r="J105" s="31" t="n">
+        <v>124956</v>
+      </c>
+      <c r="K105" s="31" t="n">
+        <v>9996480</v>
+      </c>
+      <c r="L105" s="23" t="n">
+        <v>48003520</v>
+      </c>
+      <c r="M105" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N105" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -8214,20 +10032,20 @@
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="14" t="n">
+      <c r="A107" s="28" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="B107" s="29" t="inlineStr">
         <is>
           <t>5.33.85.051.CHN.00.000</t>
         </is>
       </c>
-      <c r="C107" s="16" t="inlineStr">
+      <c r="C107" s="30" t="inlineStr">
         <is>
           <t>Phanh đuôi động cơ, model: BFK458-18E</t>
         </is>
       </c>
-      <c r="D107" s="16" t="inlineStr">
+      <c r="D107" s="30" t="inlineStr">
         <is>
           <t>Model: BFK458-18E
 Size: 18
@@ -8238,334 +10056,334 @@
 Nhà sản xuất: INTORQ</t>
         </is>
       </c>
-      <c r="E107" s="15" t="inlineStr">
+      <c r="E107" s="29" t="inlineStr">
         <is>
           <t>Intorq/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F107" s="14" t="inlineStr">
+      <c r="F107" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G107" s="17" t="n">
+      <c r="G107" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H107" s="17" t="n">
+      <c r="H107" s="31" t="n">
         <v>63063000</v>
       </c>
-      <c r="I107" s="17" t="n">
+      <c r="I107" s="31" t="n">
         <v>126126000</v>
       </c>
-      <c r="J107" s="17" t="n">
-        <v>63063000</v>
-      </c>
-      <c r="K107" s="17" t="n">
-        <v>126126000</v>
-      </c>
-      <c r="L107" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N107" s="16" t="inlineStr">
-        <is>
-          <t>5.33.85.051.CHN.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
+      <c r="J107" s="31" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="K107" s="31" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="L107" s="23" t="n">
+        <v>65366000</v>
+      </c>
+      <c r="M107" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N107" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="14" t="n">
+      <c r="A108" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="15" t="inlineStr">
+      <c r="B108" s="29" t="inlineStr">
         <is>
           <t>3.84.64.021.GER.00.000</t>
         </is>
       </c>
-      <c r="C108" s="16" t="inlineStr">
+      <c r="C108" s="30" t="inlineStr">
         <is>
           <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC</t>
         </is>
       </c>
-      <c r="D108" s="16" t="inlineStr">
+      <c r="D108" s="30" t="inlineStr">
         <is>
           <t>- Model:169800
 - Điện áp vào: 220-440VAC
 Điện áp ra: 110-205VDC</t>
         </is>
       </c>
-      <c r="E108" s="15" t="inlineStr">
+      <c r="E108" s="29" t="inlineStr">
         <is>
           <t>Siemens/ Đức</t>
         </is>
       </c>
-      <c r="F108" s="14" t="inlineStr">
+      <c r="F108" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G108" s="17" t="n">
+      <c r="G108" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H108" s="17" t="n">
+      <c r="H108" s="31" t="n">
         <v>2400000</v>
       </c>
-      <c r="I108" s="17" t="n">
+      <c r="I108" s="31" t="n">
         <v>2400000</v>
       </c>
-      <c r="J108" s="17" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="K108" s="17" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="L108" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N108" s="16" t="inlineStr">
-        <is>
-          <t>3.84.64.021.GER.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
+      <c r="J108" s="31" t="n">
+        <v>210600</v>
+      </c>
+      <c r="K108" s="31" t="n">
+        <v>210600</v>
+      </c>
+      <c r="L108" s="23" t="n">
+        <v>2189400</v>
+      </c>
+      <c r="M108" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N108" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="14" t="n">
+      <c r="A109" s="28" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="15" t="inlineStr">
+      <c r="B109" s="29" t="inlineStr">
         <is>
           <t>1.31.23.425.CHN.00.000</t>
         </is>
       </c>
-      <c r="C109" s="16" t="inlineStr">
+      <c r="C109" s="30" t="inlineStr">
         <is>
           <t>Nhớt SHELL OMALA S4 WE 220</t>
         </is>
       </c>
-      <c r="D109" s="16" t="inlineStr">
+      <c r="D109" s="30" t="inlineStr">
         <is>
           <t>Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương</t>
         </is>
       </c>
-      <c r="E109" s="15" t="inlineStr">
+      <c r="E109" s="29" t="inlineStr">
         <is>
           <t>Shell/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F109" s="14" t="inlineStr">
+      <c r="F109" s="28" t="inlineStr">
         <is>
           <t>Lít</t>
         </is>
       </c>
-      <c r="G109" s="17" t="n">
+      <c r="G109" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="H109" s="17" t="n">
+      <c r="H109" s="31" t="n">
         <v>560000</v>
       </c>
-      <c r="I109" s="17" t="n">
+      <c r="I109" s="31" t="n">
         <v>11200000</v>
       </c>
-      <c r="J109" s="17" t="n">
-        <v>560000</v>
-      </c>
-      <c r="K109" s="17" t="n">
-        <v>11200000</v>
-      </c>
-      <c r="L109" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N109" s="16" t="inlineStr">
-        <is>
-          <t>1.31.23.425.CHN.00.000 | Vật tư dung để thay thế nhớt hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="J109" s="31" t="n">
+        <v>265980</v>
+      </c>
+      <c r="K109" s="31" t="n">
+        <v>5319600</v>
+      </c>
+      <c r="L109" s="23" t="n">
+        <v>5880400</v>
+      </c>
+      <c r="M109" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N109" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="14" t="n">
+      <c r="A110" s="28" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="15" t="inlineStr">
+      <c r="B110" s="29" t="inlineStr">
         <is>
           <t>4.88.65.314.IND.00.000</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
+      <c r="C110" s="30" t="inlineStr">
         <is>
           <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945</t>
         </is>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="30" t="inlineStr">
         <is>
           <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
         </is>
       </c>
-      <c r="E110" s="15" t="inlineStr">
+      <c r="E110" s="29" t="inlineStr">
         <is>
           <t>Gea-Bgr/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F110" s="14" t="inlineStr">
+      <c r="F110" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G110" s="17" t="n">
+      <c r="G110" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H110" s="17" t="n">
+      <c r="H110" s="31" t="n">
         <v>6700000</v>
       </c>
-      <c r="I110" s="17" t="n">
+      <c r="I110" s="31" t="n">
         <v>6700000</v>
       </c>
-      <c r="J110" s="17" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="K110" s="17" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="L110" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N110" s="16" t="inlineStr">
-        <is>
-          <t>4.88.65.314.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="J110" s="31" t="n">
+        <v>904000</v>
+      </c>
+      <c r="K110" s="31" t="n">
+        <v>904000</v>
+      </c>
+      <c r="L110" s="23" t="n">
+        <v>5796000</v>
+      </c>
+      <c r="M110" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N110" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="14" t="n">
+      <c r="A111" s="28" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="B111" s="29" t="inlineStr">
         <is>
           <t>5.04.01.308.IND.00.000</t>
         </is>
       </c>
-      <c r="C111" s="16" t="inlineStr">
+      <c r="C111" s="30" t="inlineStr">
         <is>
           <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550</t>
         </is>
       </c>
-      <c r="D111" s="16" t="inlineStr">
+      <c r="D111" s="30" t="inlineStr">
         <is>
           <t>U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
         </is>
       </c>
-      <c r="E111" s="15" t="inlineStr">
+      <c r="E111" s="29" t="inlineStr">
         <is>
           <t>Gea-Bgr/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F111" s="14" t="inlineStr">
+      <c r="F111" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G111" s="17" t="n">
+      <c r="G111" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H111" s="17" t="n">
+      <c r="H111" s="31" t="n">
         <v>7300000</v>
       </c>
-      <c r="I111" s="17" t="n">
+      <c r="I111" s="31" t="n">
         <v>14600000</v>
       </c>
-      <c r="J111" s="17" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="K111" s="17" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="L111" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N111" s="16" t="inlineStr">
-        <is>
-          <t>5.04.01.308.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="J111" s="31" t="n">
+        <v>30294</v>
+      </c>
+      <c r="K111" s="31" t="n">
+        <v>60588</v>
+      </c>
+      <c r="L111" s="23" t="n">
+        <v>14539412</v>
+      </c>
+      <c r="M111" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N111" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="14" t="n">
+      <c r="A112" s="28" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="15" t="inlineStr">
+      <c r="B112" s="29" t="inlineStr">
         <is>
           <t>4.88.67.084.IND.00.000</t>
         </is>
       </c>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="C112" s="30" t="inlineStr">
         <is>
           <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945</t>
         </is>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D112" s="30" t="inlineStr">
         <is>
           <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
         </is>
       </c>
-      <c r="E112" s="15" t="inlineStr">
+      <c r="E112" s="29" t="inlineStr">
         <is>
           <t>Gea-Bgr/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F112" s="14" t="inlineStr">
+      <c r="F112" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G112" s="17" t="n">
+      <c r="G112" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H112" s="17" t="n">
+      <c r="H112" s="31" t="n">
         <v>7900000</v>
       </c>
-      <c r="I112" s="17" t="n">
+      <c r="I112" s="31" t="n">
         <v>15800000</v>
       </c>
-      <c r="J112" s="17" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="K112" s="17" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="L112" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N112" s="16" t="inlineStr">
-        <is>
-          <t>4.88.67.084.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="J112" s="31" t="n">
+        <v>1895400</v>
+      </c>
+      <c r="K112" s="31" t="n">
+        <v>3790800</v>
+      </c>
+      <c r="L112" s="23" t="n">
+        <v>12009200</v>
+      </c>
+      <c r="M112" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N112" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -8724,10 +10542,10 @@
         <v>530000000</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>265000000</v>
+        <v>271000000</v>
       </c>
       <c r="K115" s="17" t="n">
-        <v>530000000</v>
+        <v>542000000</v>
       </c>
       <c r="L115" s="17" t="n">
         <v>0</v>
@@ -8784,10 +10602,10 @@
         <v>1540000000</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>140000000</v>
+        <v>0</v>
       </c>
       <c r="K116" s="17" t="n">
-        <v>1540000000</v>
+        <v>0</v>
       </c>
       <c r="L116" s="17" t="n">
         <v>0</v>
@@ -8821,10 +10639,10 @@
       </c>
       <c r="J117" s="35" t="n"/>
       <c r="K117" s="36" t="n">
-        <v>32385281416.5</v>
+        <v>31370614665.5</v>
       </c>
       <c r="L117" s="37" t="n">
-        <v>5937874583.5</v>
+        <v>1292573334.5</v>
       </c>
       <c r="M117" s="35" t="n"/>
       <c r="N117" s="35" t="n"/>
@@ -8846,9 +10664,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N107" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N108" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N112" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8860,7 +10709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8976,12 +10825,12 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN CÔNG NGHỆ CƠ ĐIỆN EME báo giá 15,592,850 đ (+15.0%)</t>
+          <t xml:space="preserve">Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 16,000,000 </t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.00</t>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 11.842.500 đ/Cái (dao động từ 6.015.000 đ đến 17.670.000 đ). Đơn giá trình đợt này là 13.559.000 đ/Cái (+14.5% s</t>
         </is>
       </c>
       <c r="H5" s="40" t="inlineStr">
@@ -8989,15 +10838,12 @@
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [908531], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I5" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Module đầu vào input IUX 760 MI] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
+      <c r="I5" s="40" t="inlineStr"/>
       <c r="J5" s="40" t="inlineStr"/>
       <c r="K5" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 6.015.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
 (Tiết kiệm: 30.176.000 đ)</t>
         </is>
       </c>
@@ -9038,15 +10884,12 @@
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I6" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
+      <c r="I6" s="40" t="inlineStr"/>
       <c r="J6" s="40" t="inlineStr"/>
       <c r="K6" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 7.000.000 đ
+(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (QĐ 161))
 (Tiết kiệm: 7.208.000 đ)</t>
         </is>
       </c>
@@ -9107,6 +10950,7 @@
       <c r="K7" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 16.491.600 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web (Landed Cost DDP VT4))
 (Tiết kiệm: 197.542.000 đ)</t>
         </is>
       </c>
@@ -9128,10 +10972,7 @@
 Loại van: Van điều khiển ống dẫn (spool control valve) được vận hành bằng khí nén (pilot-operated).
 Điện áp: 24 VAC.
 Cổng kết nối: 1/4" NPT.
-Áp suất hoạt động: 35 đến 150 psig (2.4 đến 10.3 bar) với không khí đã lọc.
-Nhiệt độ hoạt động: 0°F đến 123°F (-18°C đến 50°C).
-Gắn kết: Gắn trực tiếp giao diện NAMUR.
-Nhà sản xuất: Bray International.)</t>
+Áp suất hoạt động: 35 đến 150 psig (2.4 đế</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr"/>
@@ -9168,6 +11009,7 @@
       <c r="K8" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 9.009.300 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
 (Tiết kiệm: 274.953.500 đ)</t>
         </is>
       </c>
@@ -9225,6 +11067,7 @@
       <c r="K9" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.500.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9264,11 +11107,7 @@
           <t>Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4, các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn g</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 07/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [GEFA DG1], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện tro</t>
-        </is>
-      </c>
+      <c r="H10" s="40" t="inlineStr"/>
       <c r="I10" s="40" t="inlineStr">
         <is>
           <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [GEFA DG1], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụ</t>
@@ -9282,6 +11121,7 @@
       <c r="K10" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 8.910.000 đ
+(Cơ sở 3: EVN IMIS Toàn Ngành)
 (Tiết kiệm: 52.340.000 đ)</t>
         </is>
       </c>
@@ -9344,6 +11184,7 @@
       <c r="K11" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 452.147.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9409,6 +11250,7 @@
       <c r="K12" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 620.000 đ
+(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (HĐ 03/2022))
 (Tiết kiệm: 3.840.000 đ)</t>
         </is>
       </c>
@@ -9470,6 +11312,7 @@
       <c r="K13" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.315.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9531,6 +11374,7 @@
       <c r="K14" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.508.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9600,6 +11444,7 @@
       <c r="K15" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 113.232.916 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
 (Tiết kiệm: 4.367.084 đ)</t>
         </is>
       </c>
@@ -9641,22 +11486,23 @@
       </c>
       <c r="H16" s="40" t="inlineStr">
         <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-T6-S-065-20], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát đi</t>
+        </is>
+      </c>
+      <c r="I16" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+        </is>
+      </c>
+      <c r="J16" s="40" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
-        </is>
-      </c>
-      <c r="J16" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K16" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 18.522.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 27.230.000 đ)</t>
         </is>
       </c>
@@ -9667,14 +11513,13 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>3.96.13.320.USA.00.000</t>
+          <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-(Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-NSX: MERRICK)</t>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m
+(Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -9689,33 +11534,30 @@
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (56,105,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 4). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN H</t>
+          <t>Đơn giá trình (19,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
         </is>
       </c>
       <c r="G17" s="40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 12.350.000 đ/Cái (dao động từ 5.400.000 đ đến 19.300.000 đ). Đơn giá trình đợt này là 19.000.000 đ/Cái (+53.8% s</t>
+        </is>
+      </c>
+      <c r="H17" s="40" t="inlineStr"/>
       <c r="I17" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:43 ngày 09/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 21.230.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
         </is>
       </c>
       <c r="J17" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thư</t>
         </is>
       </c>
       <c r="K17" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 23.000.000 đ
-(Tiết kiệm: 66.210.000 đ)</t>
+          <t>Đơn giá chốt: 12.350.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 13.300.000 đ)</t>
         </is>
       </c>
     </row>
@@ -9725,23 +11567,13 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>Chưa có mã vật tư</t>
+          <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
       <c r="C18" s="40" t="inlineStr">
         <is>
-          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than
-(Lining Plate (Compound Armour Plate)
-Tấm lót thân máy nghiền
-Bao gồm 106 chi tiết (tấm)
-Chế tạo bằng thép Kalmetall W100/Kalenborn
-- Vật liệu: Thép 2 thành phần Kalmetall W100 - Kalenborn
-- Độ dày: 16mm ( 8+8 )
-- Độ dày: 10mm ( 6+4 )
-- Thép nền S235JRG2
-- Lớp phủ hợp kim Chromium Carbides: %C~5; %Cr~30; %Fe + others Balance 
-- Độ cứng ~ 700HV trên toàn bộ lớp phủ
-- Chống mài mòn theo ASTM G65: 0,0060 mm3/m)</t>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6
+(Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -9756,42 +11588,1377 @@
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>CẢNH BÁO: Đơn giá trình (2,618,304,000 đ) lấy từ Báo giá của DTL 19.8.2026. xlsx nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 1,300,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO G</t>
+          <t>Đơn giá trình (1,700,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,150,000 đ (+26.</t>
         </is>
       </c>
       <c r="G18" s="40" t="inlineStr">
         <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ</t>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.03.2022 (ngày ký 2022-03-07 00:00:00, do Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.</t>
         </is>
       </c>
       <c r="H18" s="40" t="inlineStr">
         <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-810-6], vật tư có lịch sử mua sắm tương đương tại Công ty Dịch vụ sửa chữa các nhà máy điện EVNGENCO3 (t</t>
         </is>
       </c>
       <c r="I18" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J18" s="40" t="inlineStr"/>
+          <t>Đã tra cứu từ khóa [SS-810-6] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:46 ngày 09/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 1.319.000 đ (Mã TBMT: IB2600209753, Bên mời thầu: CÔNG TY N</t>
+        </is>
+      </c>
+      <c r="J18" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các t</t>
+        </is>
+      </c>
       <c r="K18" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 1.300.000 đ
-(Tiết kiệm: 5.234.008.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>Đơn giá chốt: 1.319.000 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 762.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
       <c r="A19" s="38" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
+          <t>4.82.22.025.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6
+(Đầu nối - Union Swagelok Model: SS-600-6)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,600,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LO</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 25/2025) theo hóa đơn số 00000091 ngày 24.06.2025 (ngày ký 2025-07-24 00:00:00) với đơn giá 2.600.000 đ/Cái (Tổng số 6 đợt mua sắm lịch sử có đơn giá dao động từ 630.0</t>
+        </is>
+      </c>
+      <c r="H19" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-600-6], vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn (thời gian N/A) v</t>
+        </is>
+      </c>
+      <c r="I19" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-600-6] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 14:35 ngày 13/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 794.090 đ (Mã TBMT: IB2400563322, Bên mời thầu: CÔNG TY NHI</t>
+        </is>
+      </c>
+      <c r="J19" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6] trên thị trường Thương mại điện tử / Website nhà cung cấp (Ảnh chụp màn hình web) tại đường link [https://www.ebay.</t>
+        </is>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 644.760 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 195.524.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001
+(Bộ điều khiển định vị Positioner:
+- Model: TZIDC-V18345- 2020521001
+-Type: Double acting 
+-Sofw.Rev: 3 
+-Supply press: 1,4 ~ 6 bar 
+-Input: Analog 4 ~ 20 mA
+ -Loss of electric: Fail freeze
+- Option: Analog feedback, FSK, Position indicator 
+-NSX: ABB)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (85,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2026 (ngày ký 2026-06-03 00:00:00, do Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [TZIDC], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Cần Thơ (thời gian N/A) với đơn giá 83</t>
+        </is>
+      </c>
+      <c r="I20" s="40" t="inlineStr"/>
+      <c r="J20" s="40" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 83.484.000 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 7.580.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire
+(Cảm biến nhiệt độ - Model: S14405PD3S350B0
+- NSX: MINCO 
+- Element: Platinum 
+- Element length: 6.4 mm 
+- Cable dimension "C": 1778 mm 
+- Cable dimension "L": 8890 mm 
+- Single duplex: Duplex 
+- Sheath: 2.9 mm OD 
+- Type: RTD PT100, 3 Wire 
+- Range: 0 - 260 °C)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (30,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ngày 15.06.2026 (ngày ký 2026-07-22 00:00:00, do Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ng</t>
+        </is>
+      </c>
+      <c r="H21" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTD PT100], vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Thủy điện Thác Mơ (thời gian N/A) </t>
+        </is>
+      </c>
+      <c r="I21" s="40" t="inlineStr"/>
+      <c r="J21" s="40" t="inlineStr"/>
+      <c r="K21" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 27.923.445 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 2.076.555 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)
+(LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
+Range: 0.5m to 15m Signal: 4 - 20 mA 
+Supply power: 115 to 230 V AC or 24 V DC.
+NSX: ABB)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (189,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG </t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4. Căn cứ đơn giá sẽ được thẩm định và xác định dựa trên Báo giá mới nhận (Khối 1), CSDL IMIS EVN (Khối 3) và Mua Sắm Công (Khối 4)</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [LST400], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
+        </is>
+      </c>
+      <c r="I22" s="40" t="inlineStr"/>
+      <c r="J22" s="40" t="inlineStr"/>
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 75.764.141 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 113.235.859 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+(Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+Model: MA3145-230-2-R
+- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
+- Điện áp định mức (Voltage rating): 230 VAC.
+- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
+NSX: Cooper Crouse-Hinds MTL / Eaton)</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (35,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4, các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn g</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [MA3145], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
+        </is>
+      </c>
+      <c r="I23" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [MTL], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CS</t>
+        </is>
+      </c>
+      <c r="J23" s="40" t="inlineStr"/>
+      <c r="K23" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 21.609.600 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 40.171.200 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>3.34.40.009.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)
+(Công tắc lưu lượng (Flow Switch)
+Model: WP/FS-25VFL
+Switch : SPDT Snap Acting Micro
+Rating : 5A 250VAC 
+NSX: Dag Process Instruments Pvt. Ltd)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (38,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 32.500.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 12/2025) theo hóa đơn số 00000036 ngày 24.03.2025 ngày 2025-03-27. SL: 1 Cái)</t>
+        </is>
+      </c>
+      <c r="H24" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Công tắc lưu lượng], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I24" s="40" t="inlineStr"/>
+      <c r="J24" s="40" t="inlineStr"/>
+      <c r="K24" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 32.500.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 5.500.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+(Cảm biến tiệm cận/proximity sensor
+- Model: PR30-10AC
+Đường kính cạnh phát hiện: 30mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NC
+- Protection: IP67)</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (1,219,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 6). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,000,000 đ (+64.1%).</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 598.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:123/2022) theo hóa đơn số 993. 994 ngày 26.12.2022 ngày 2022-12-27. SL: 1 Cái)</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR30], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Mông Dương (thời gian N/A) với đơn giá </t>
+        </is>
+      </c>
+      <c r="I25" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Autonics] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 08:23 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 382.320 đ (Mã TBMT: IB2600205775, Bên mời thầu: CÔNG TY THỦ</t>
+        </is>
+      </c>
+      <c r="J25" s="40" t="inlineStr"/>
+      <c r="K25" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 911.127 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 615.746 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+(Cảm biến tiệm cận/proximity sensor
+- Model: PR18-8AO
+- Đường kính đầu dò: 18mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NO
+- Protection: IP67)</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (1,150,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,600,000 đ (+39.1%).</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có 3 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 598.667 đ/Cái (dao động từ 528.000 đ đến 740.000 đ). Đơn giá trình đợt này là 1.150.000 đ/Cái (+92.1% so với đơn</t>
+        </is>
+      </c>
+      <c r="H26" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR18], vật tư có lịch sử mua sắm tương đương tại Công ty TNHH MTV Thủy điện Trung Sơn (thời gian N/A) với đ</t>
+        </is>
+      </c>
+      <c r="I26" s="40" t="inlineStr"/>
+      <c r="J26" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor - Model: PR18-8AO - Đường kính đầu dò: 18mm - Điện áp hoạt động: 100-240 Vac - Ngõ ra điều khiển: NO - Protection: IP67] trên th</t>
+        </is>
+      </c>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 577.200 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 572.800 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713
+(Pendant control station:
+Type: XAC-A12713)</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (5,784,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 6,000,000 đ (+3.7%). </t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 2.369.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000011 ngày 22.01.2024 ngày 2024-02-27. SL: 6 Cái)</t>
+        </is>
+      </c>
+      <c r="H27" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [XAC-A12713], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I27" s="40" t="inlineStr"/>
+      <c r="J27" s="40" t="inlineStr"/>
+      <c r="K27" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 420.000 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 5.364.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)
+(Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+- Material: PVC
+- Maker: Eunchang T&amp;C)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (66,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 82,000 đ (+24.2%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 26.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 300 Cái); Các đợt nhập khác: 24.800 đ, 80.000 đ</t>
+        </is>
+      </c>
+      <c r="H28" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bao che giữa các], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I28" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Bao che giữa các khớp nối đường ray cáp điện (Joint cover)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J28" s="40" t="inlineStr"/>
+      <c r="K28" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 26.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 9.400.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)
+(Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+- Maker: Eunchang T&amp;C)</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (68,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 76,000 đ (+11.8%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 21.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 32 Cái); Các đợt nhập khác: 18.000 đ, 710.000 đ</t>
+        </is>
+      </c>
+      <c r="H29" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Nắp che phía cuối], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I29" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Nắp che phía cuối đường ray cáp điện (End cap)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J29" s="40" t="inlineStr"/>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 21.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 1.504.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)
+(Trolley-bar (thanh ray cấp nguồn):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Length: 3m / cây
+- Material: Copper
+- Maker: EunchangT&amp;C)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (909,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,020,000 đ (+12.2%). Đ</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.09.2023 (ngày ký 2023-09-25 00:00:00, do Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.</t>
+        </is>
+      </c>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Trolley bar (thanh ray], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I30" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Trolley-bar], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp</t>
+        </is>
+      </c>
+      <c r="J30" s="40" t="inlineStr"/>
+      <c r="K30" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 890.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 532.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.133.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913
+(Pendant control station:
+Type: XAC-A6913
+Control station composition: 06 push buttons + 01 emergency stop
+Product compatibility: 
+ZB2BE102 for emergency stop, XEN-G1191 for each direction
+Color: Yellow)</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (13,319,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 14,670,000 đ (+10.1%</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr"/>
+      <c r="H31" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [A6913], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
+        </is>
+      </c>
+      <c r="I31" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [XAC] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:08 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 3.290.400 đ (Mã TBMT: IB2600015122, Bên mời thầu: CHI NHÁNH TỔNG</t>
+        </is>
+      </c>
+      <c r="J31" s="40" t="inlineStr"/>
+      <c r="K31" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 3.290.400 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 10.028.600 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="38" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
+(Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm)</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (610,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 716,000 đ của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf).</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 (ngày ký 2024-09-06 00:00:00, do Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 </t>
+        </is>
+      </c>
+      <c r="H32" s="40" t="inlineStr"/>
+      <c r="I32" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Lưỡi gà móc cẩu] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:18 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 314.600 đ (Mã TBMT: IB2300214547, Bên mời thầu: CÔNG</t>
+        </is>
+      </c>
+      <c r="J32" s="40" t="inlineStr"/>
+      <c r="K32" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 314.600 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 295.400 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm
+(Cáp inox 304 
+Kích thước: Ø 3 mm)</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (37,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 41,000 đ (+10.8%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 86.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 90 Mét); Các đợt nhập khác: 67.000 đ, 12.000 đ</t>
+        </is>
+      </c>
+      <c r="H33" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cáp inox 304 Kích], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I33" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 10.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J33" s="40" t="inlineStr"/>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 24.000 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 780.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm
+(Phe cài trục ngoài cho đường kính 28mm.
+Vật liệu: Inox 304)</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (56,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 67,000 đ (+19.6%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 50.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:43) theo hóa đơn số 0000015 ngày 21.06.2021 ngày 2021-06-26. SL: 201 Cái); Các đợt nhập khác: 48.400 đ, 371.800 đ</t>
+        </is>
+      </c>
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Phe cài trục ngoài], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I34" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Phe cài trục ngoài cho đường kính 28mm] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J34" s="40" t="inlineStr"/>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 50.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 6.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+(Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan)</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,254,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 3,670,000 đ (+62.8%).</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lịch sử nhập kho ERP Vĩnh Tân 4 [Kẹp cố định đầu ray. Loại: CH2260. Size: 80x51x3mm. Vật liệu: Inox 304]: 3.574.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: </t>
+        </is>
+      </c>
+      <c r="H35" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [2.06.60.080.TPE.00.000], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I35" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 578.078 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J35" s="40" t="inlineStr"/>
+      <c r="K35" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 578.078 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 3.351.844 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+(Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+Điện áp: 450/750V
+Cách điện: PVC, dẻo
+NSX: Imatek)</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (711,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 780,000 đ (+9.7%). Đơn </t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Cáp điện dẹt cho cầu trục. 16mm2 x 4C]: 1.091.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 99 Mét); Các đợt nhập khác: 730.0</t>
+        </is>
+      </c>
+      <c r="H36" s="40" t="inlineStr">
+        <is>
+          <t>IMIS EVN: 76.000 đ/Cái (Trung tâm Dịch vụ sửa chữa EVN - Chi nhánh Tập đoàn Điện lực Việt Nam)</t>
+        </is>
+      </c>
+      <c r="I36" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 125.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J36" s="40" t="inlineStr"/>
+      <c r="K36" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 76.000 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 31.750.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm
+(Khóa cáp 
+Dùng cho cáp: 3mm)</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (20,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 31,000 đ (+55.0%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Khóa cáp dùng cho cáp 3mm]: 14.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 108 Cái); Các đợt nhập khác: 38.000 đ, 14.000 đ</t>
+        </is>
+      </c>
+      <c r="H37" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Khóa cáp Dùng cho], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I37" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 5.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J37" s="40" t="inlineStr"/>
+      <c r="K37" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 14.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 330.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+(Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+Control station composition: 06, push buttons + 01 emergency stop)</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (7,406,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 8,000,000 đ (+8.0%). </t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Pendant control station. Type: XACA6713]: 6.600.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 65/2024) theo hóa đơn số 00000031 ngày 18.09.2024 ngày 2024-10-09. SL: 10 Cái); Các đợt nhập khác: 1.71</t>
+        </is>
+      </c>
+      <c r="H38" s="40" t="inlineStr">
+        <is>
+          <t>IMIS EVN: 3.310.185 đ/Cái (Công ty Nhiệt điện Vĩnh Tân)</t>
+        </is>
+      </c>
+      <c r="I38" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Pendant control station (Tay bấm điều khiển tời điện):] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J38" s="40" t="inlineStr"/>
+      <c r="K38" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 3.310.185 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 4.095.815 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn
+(Lưỡi gà móc cẩu 7 tấn:
+ + Kích thước: 60 x 175x 3mm
+ + Vật liệu: thép)</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (656,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 712,000 đ (+8.5%). Đơn </t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Lưỡi gà móc cẩu BCD10t. Kích thước (DxR): 120mmx41mm]: 585.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 ngày 2024-09-06. SL: 1 Cái); Các đợt nhập khác:</t>
+        </is>
+      </c>
+      <c r="H39" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Lưỡi gà móc cẩu], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I39" s="40" t="inlineStr"/>
+      <c r="J39" s="40" t="inlineStr"/>
+      <c r="K39" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 585.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 71.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN
+(Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPN
+- PR (Product Revision): M)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (21,120,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 25,200,000 </t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 05.01.2022 (ngày ký 2022-01-05 00:00:00, do Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 0</t>
+        </is>
+      </c>
+      <c r="H40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 19.360.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 52.800.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>5.01.07.302.FRA.00.000</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302
+(Bạc đạn 6302)</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (158,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 200,000 đ (+26.6%). Đơn</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:223) theo BB giao nhận và BB nghiệm thu kĩ thuật ngày 30.12.2020 (ngày ký 2020-12-31 00:00:00, do Nhập kho vật tư (HĐ:223) theo BB giao nhận và B</t>
+        </is>
+      </c>
+      <c r="H41" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bạc đạn 6302 Bạc], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I41" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 43.805 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J41" s="40" t="inlineStr"/>
+      <c r="K41" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 85.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 146.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="38" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
++ Cycloidal Gear Reducer Type: 
+XLD3-59-1.1KW
+(Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
++ Cycloidal Gear Reducer Type: 
+XLD3-59-1.1KW
++ Input Power: 1.1 KW
++ Transmission Ratio: 59
++ Nhà sản xuất: JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (58,240,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 60,127,000 đ (+3.2%)</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000141 ngày 27.12.2023 (ngày ký 2023-12-29 00:00:00, do Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000141 ngày 2</t>
+        </is>
+      </c>
+      <c r="H42" s="40" t="inlineStr"/>
+      <c r="I42" s="40" t="inlineStr"/>
+      <c r="J42" s="40" t="inlineStr"/>
+      <c r="K42" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 56.900.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 1.340.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="38" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW
 (Bơm (SP-Circulation pump):
@@ -9809,41 +12976,428 @@
 IEC60034-1)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>[Lưu trong hồ sơ PDF]</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F43" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">CẢNH BÁO: Đơn giá trình (770,000,000 đ) lấy từ Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 750,000,000 đ của 08-27-26. BV-VT 4. . 1,620,000,000 </t>
         </is>
       </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="G43" s="40" t="inlineStr">
         <is>
           <t>Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.</t>
         </is>
       </c>
-      <c r="H19" s="40" t="inlineStr">
+      <c r="H43" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I19" s="40" t="inlineStr">
+      <c r="I43" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J19" s="40" t="inlineStr"/>
-      <c r="K19" s="41" t="inlineStr">
+      <c r="J43" s="40" t="inlineStr"/>
+      <c r="K43" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 750.000.000 đ
+(Cơ sở 1: Đàm phán giảm giá / Báo giá chào)
 (Tiết kiệm: 40.000.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>4.31.28.586.JPN.99.000</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm
+(Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương)</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (725,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf, Trang 2). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 19/2025) theo hóa đơn số 00000020 ngày 25.03.2025 (ngày ký 2025-03-28 00:00:00) với đơn giá 950.000 đ/Cái (Tổng số 2 đợt mua sắm lịch sử có đơn giá dao động từ 282.000</t>
+        </is>
+      </c>
+      <c r="H44" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [Que hàn TIG AWS], vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Nhiệt điện Hải Phòng (thời gian</t>
+        </is>
+      </c>
+      <c r="I44" s="40" t="inlineStr"/>
+      <c r="J44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 124.956 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 48.003.520 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="38" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>5.33.85.051.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Phanh đuôi động cơ, model: BFK458-18E
+(Model: BFK458-18E
+Size: 18
+Đường kính phủ bì: 218,6mm
+Lỗ lắp bulong: 6xM8
+Đường kính vòng chia bulong: 196mm
+Điện áp: 205VDC
+Nhà sản xuất: INTORQ)</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E45" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (63,063,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file 4.9 Báo giá Thăng Long bổ sung.pdf, Trang 1). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂN</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:136/2021) theo hóa đơn số 466, 467 ngày 12.07.2022 (ngày ký 2022-07-28 00:00:00, do Nhập kho vật tư (HĐ:136/2021) theo hóa đơn số 466, 467 ngày 1</t>
+        </is>
+      </c>
+      <c r="H45" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [BFK458], vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Thủy điện Sông Ba Hạ (thời gian N/A) với</t>
+        </is>
+      </c>
+      <c r="I45" s="40" t="inlineStr"/>
+      <c r="J45" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 30.380.000 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 65.366.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="38" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>3.84.64.021.GER.00.000</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC
+(- Model:169800
+- Điện áp vào: 220-440VAC
+Điện áp ra: 110-205VDC)</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,400,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 4,700,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf).</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="40" t="inlineStr"/>
+      <c r="J46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 210.600 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 2.189.400 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="38" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>1.31.23.425.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220
+(Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương)</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (560,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file 4.9 Báo giá Thăng Long bổ sung.pdf, Trang 1). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG L</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 14/2025) theo hóa đơn số 00000086 ngày 18.04.2025 (ngày ký 2025-05-07 00:00:00, do Nhập kho vật tư (HĐ: 14/2025) theo hóa đơn số 00000086 ngày 1</t>
+        </is>
+      </c>
+      <c r="H47" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SHELL OMALA S4], vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn (thời gian </t>
+        </is>
+      </c>
+      <c r="I47" s="40" t="inlineStr"/>
+      <c r="J47" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 265.980 đ
+(Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4)
+(Tiết kiệm: 5.880.400 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>4.88.65.314.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C48" s="40" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945
+(Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương)</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E48" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (6,700,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf, Trang 3). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THU</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 08/2025) theo hóa đơn số 00000040 ngày 17.04.2025 (ngày ký 2025-04-29 00:00:00) với đơn giá 6.800.000 đ/Cái (Tổng số 2 đợt mua sắm lịch sử có đơn giá dao động từ 3.995</t>
+        </is>
+      </c>
+      <c r="H48" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [21336], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
+        </is>
+      </c>
+      <c r="I48" s="40" t="inlineStr"/>
+      <c r="J48" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 904.000 đ
+(Cơ sở 1: Báo Giá Gốc)
+(Tiết kiệm: 5.796.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>5.04.01.308.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550
+(U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương)</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (7,300,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf, Trang 3). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THU</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 08/2025) theo hóa đơn số 00000045 ngày 24.04.2025 (ngày ký 2025-05-12 00:00:00, do Nhập kho vật tư (HĐ: 08/2025) theo hóa đơn số 00000045 ngày 2</t>
+        </is>
+      </c>
+      <c r="H49" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [21338], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
+        </is>
+      </c>
+      <c r="I49" s="40" t="inlineStr"/>
+      <c r="J49" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 30.294 đ
+(Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4)
+(Tiết kiệm: 14.539.412 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>4.88.67.084.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945
+(Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương)</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E50" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (7,900,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf, Trang 3). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THU</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 09/2026) theo hóa đơn số 00000124 ngày 25.02.2026 (ngày ký 2026-02-26 00:00:00, do Nhập kho vật tư (HĐ: 09/2026) theo hóa đơn số 00000124 </t>
+        </is>
+      </c>
+      <c r="H50" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [21340], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
+        </is>
+      </c>
+      <c r="I50" s="40" t="inlineStr"/>
+      <c r="J50" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 1.895.400 đ
+(Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4)
+(Tiết kiệm: 12.009.200 đ)</t>
         </is>
       </c>
     </row>
@@ -9851,8 +13405,14 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -3701,7 +3701,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 14/09/2026 21:31</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 14/09/2026 21:51</t>
         </is>
       </c>
     </row>

--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Báo Cáo Tổng Hợp" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Danh Mục Chi Tiết" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Hồ Sơ Chứng Cứ &amp; Hình Ảnh" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Đối Soát Giảm Giá &amp; Thời Hạn" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="16">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,8 +118,26 @@
       <color rgb="0015803D"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00E0F2FE"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00FEF3C7"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +180,22 @@
         <bgColor rgb="00CBD5E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000369A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092400E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -186,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,6 +377,31 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7781,7 +7843,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Hồ sơ: Mau_Bang_Du_Toan_13_Cot - Bản Mới-111 | Cập nhật: 18/09/2026 14:28</t>
+          <t>Hồ sơ: Mau_Bang_Du_Toan_13_Cot - Bản Mới-111 | Cập nhật: 18/09/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -21319,4 +21381,1861 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>BẢNG ĐỐI SOÁT QUY CÁCH KỸ THUẬT &amp; ĐÁNH GIÁ HIỆU LỰC THỜI GIAN CÁC MỤC GIẢM GIÁ DỰ TOÁN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Mục tiêu 1: So sánh Quy cách, Thông số, Model | Mục tiêu 2: Đánh giá mốc thời gian cơ sở đơn giá quá 12 tháng theo Quy định EVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Mã ERP</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Tên Vật Tư Trình Duyệt</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>ĐVT</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Đơn Giá Trình (đ)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Thành Tiền Trình (đ)</t>
+        </is>
+      </c>
+      <c r="H4" s="61" t="inlineStr">
+        <is>
+          <t>Quy Cách, Model TRÌNH DUYỆT</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Cơ Sở Đơn Giá Thẩm Định</t>
+        </is>
+      </c>
+      <c r="J4" s="61" t="inlineStr">
+        <is>
+          <t>Quy Cách, Model CƠ SỞ ĐƠN GIÁ</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Đơn Giá Thống Nhất (đ)</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Thành Tiền Thống Nhất (đ)</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Giá Trị Giảm (đ)</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>% Giảm</t>
+        </is>
+      </c>
+      <c r="O4" s="61" t="inlineStr">
+        <is>
+          <t>[MỤC TIÊU 1] Đánh Giá Quy Cách &amp; Model</t>
+        </is>
+      </c>
+      <c r="P4" s="62" t="inlineStr">
+        <is>
+          <t>Số HĐ / Báo Giá / Quyết Định Cơ Sở</t>
+        </is>
+      </c>
+      <c r="Q4" s="62" t="inlineStr">
+        <is>
+          <t>Ngày Cơ Sở Đơn Giá</t>
+        </is>
+      </c>
+      <c r="R4" s="62" t="inlineStr">
+        <is>
+          <t>Ngày Thẩm Định</t>
+        </is>
+      </c>
+      <c r="S4" s="62" t="inlineStr">
+        <is>
+          <t>Thời Gian (Tháng)</t>
+        </is>
+      </c>
+      <c r="T4" s="62" t="inlineStr">
+        <is>
+          <t>[MỤC TIÊU 2] Đánh Giá Hiệu Lực (Mốc 12T)</t>
+        </is>
+      </c>
+      <c r="U4" s="13" t="inlineStr">
+        <is>
+          <t>Ghi Chú &amp; Thuyết Minh Thẩm Định</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng V phân phối mạ bạc</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>Thanh</t>
+        </is>
+      </c>
+      <c r="E5" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng V phân phối mạ bạc
+Kích thước: 28x40x6mm
+Chiều dài: 920mm - Hãng: Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>Thanh đồng mạ niken, KT: 30x600x5mm | Thanh đồng mạ niken, KT: 30x600x5mm</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>1390909</v>
+      </c>
+      <c r="L5" s="27" t="n">
+        <v>5563636</v>
+      </c>
+      <c r="M5" s="64" t="n">
+        <v>186436364</v>
+      </c>
+      <c r="N5" s="65" t="n">
+        <v>97.10227291666666</v>
+      </c>
+      <c r="O5" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P5" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ:227) theo hóa đơn số 0000035 ngày 15.01.2021</t>
+        </is>
+      </c>
+      <c r="Q5" s="24" t="inlineStr">
+        <is>
+          <t>25/01/2021</t>
+        </is>
+      </c>
+      <c r="R5" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S5" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="T5" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (68 tháng - 5.7 năm)</t>
+        </is>
+      </c>
+      <c r="U5" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 1,390,909 đ (giảm trừ 46,609,091 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Kungho/ Trung Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN125</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E6" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>9660000</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>19320000</v>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN125, 8 lỗ bulong Ø16 ở mỗi đầu bích;
+Vật liệu: Cast iron;
+Môi chất làm việc: nước sạch (nước khử khoáng);
+Công tơ có giấy chứng nhận hiệu chuẩn. - Hãng: Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>Khớp nối mềm; SREJ-0125-16-D2R; DN125mm; PN16bar | Đơn vị: Công ty Thủy điện Buôn Kuốp</t>
+        </is>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>1972455</v>
+      </c>
+      <c r="L6" s="27" t="n">
+        <v>3944910</v>
+      </c>
+      <c r="M6" s="64" t="n">
+        <v>15375090</v>
+      </c>
+      <c r="N6" s="65" t="n">
+        <v>79.58121118012423</v>
+      </c>
+      <c r="O6" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P6" s="26" t="inlineStr">
+        <is>
+          <t>2603/2025/VTN_15</t>
+        </is>
+      </c>
+      <c r="Q6" s="24" t="inlineStr">
+        <is>
+          <t>26/03/2025</t>
+        </is>
+      </c>
+      <c r="R6" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (18 tháng - 1.5 năm)</t>
+        </is>
+      </c>
+      <c r="U6" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 1,972,455 đ (giảm trừ 7,687,545 đ/đơn vị) căn cứ theo Cơ sở 3: EVN IMIS, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (DN125 - Zenner/ Trung Quốc). LÝ DO KỸ THUẬT KHÔNG ÁP D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>5.05.65.658.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Collector (chổi tiếp điện từ thanh ray)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="E7" s="63" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>2265000</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>81540000</v>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>Collector (chổi tiếp điện từ thanh ray):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Material: Copper
+- Maker: Eunchang T&amp;C - Hãng: Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>Chổi tiếp điện từ thanh ray (Electric collector); 60A; 400VAC.</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="L7" s="27" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="M7" s="64" t="n">
+        <v>18540000</v>
+      </c>
+      <c r="N7" s="65" t="n">
+        <v>22.73730684326711</v>
+      </c>
+      <c r="O7" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P7" s="26" t="inlineStr">
+        <is>
+          <t>IB2600422382</t>
+        </is>
+      </c>
+      <c r="Q7" s="24" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="R7" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S7" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="68" t="inlineStr">
+        <is>
+          <t>🟢 Trong hạn 12 tháng (0 tháng)</t>
+        </is>
+      </c>
+      <c r="U7" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 1,750,000 đ (giảm trừ 515,000 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Eunchang/ Hàn Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E8" s="63" t="n">
+        <v>235</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>15510000</v>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+- Material: PVC
+- Maker: Eunchang T&amp;C - Hãng: Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>57000</v>
+      </c>
+      <c r="L8" s="27" t="n">
+        <v>13395000</v>
+      </c>
+      <c r="M8" s="64" t="n">
+        <v>2115000</v>
+      </c>
+      <c r="N8" s="65" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="O8" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P8" s="26" t="inlineStr">
+        <is>
+          <t>IB2600422382</t>
+        </is>
+      </c>
+      <c r="Q8" s="24" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="R8" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="68" t="inlineStr">
+        <is>
+          <t>🟢 Trong hạn 12 tháng (0 tháng)</t>
+        </is>
+      </c>
+      <c r="U8" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 57,000 đ (giảm trừ 9,000 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Eunchang/ Hàn Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E9" s="63" t="n">
+        <v>32</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>68000</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>2176000</v>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+- Maker: Eunchang T&amp;C - Hãng: Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover) | Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>832000</v>
+      </c>
+      <c r="M9" s="64" t="n">
+        <v>1344000</v>
+      </c>
+      <c r="N9" s="65" t="n">
+        <v>61.76470588235294</v>
+      </c>
+      <c r="O9" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P9" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr">
+        <is>
+          <t>27/02/2023</t>
+        </is>
+      </c>
+      <c r="R9" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S9" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="T9" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (43 tháng - 3.6 năm)</t>
+        </is>
+      </c>
+      <c r="U9" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 26,000 đ (giảm trừ 42,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Eunchang/ Hàn Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Cây</t>
+        </is>
+      </c>
+      <c r="E10" s="63" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>909000</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>25452000</v>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Length: 3m / cây
+- Material: Copper
+- Maker: EunchangT&amp;C - Hãng: Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap) | Nắp che phía cuối đường ray cáp điện (End cap)</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>21000</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>588000</v>
+      </c>
+      <c r="M10" s="64" t="n">
+        <v>24864000</v>
+      </c>
+      <c r="N10" s="65" t="n">
+        <v>97.6897689768977</v>
+      </c>
+      <c r="O10" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P10" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023</t>
+        </is>
+      </c>
+      <c r="Q10" s="24" t="inlineStr">
+        <is>
+          <t>27/02/2023</t>
+        </is>
+      </c>
+      <c r="R10" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S10" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="T10" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (43 tháng - 3.6 năm)</t>
+        </is>
+      </c>
+      <c r="U10" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 21,000 đ (giảm trừ 888,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Eunchang/ Hàn Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>610000</v>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm - Hãng: MT/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu BCD10t, Kích thước (DxR): 120mmx41mm | Lưỡi gà móc cẩu BCD10t, Kích thước (DxR): 120mmx41mm</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>585000</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>585000</v>
+      </c>
+      <c r="M11" s="64" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N11" s="65" t="n">
+        <v>4.098360655737705</v>
+      </c>
+      <c r="O11" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P11" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024</t>
+        </is>
+      </c>
+      <c r="Q11" s="24" t="inlineStr">
+        <is>
+          <t>06/09/2024</t>
+        </is>
+      </c>
+      <c r="R11" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S11" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (24 tháng - 2.0 năm)</t>
+        </is>
+      </c>
+      <c r="U11" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 585,000 đ (giảm trừ 25,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - MT/ Trung Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="E12" s="63" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>711000</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>35550000</v>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+Điện áp: 450/750V
+Cách điện: PVC, dẻo
+NSX: Imatek - Hãng: Imatek/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="inlineStr">
+        <is>
+          <t>Ống nối cáp điện; model: SL16, chất liệu đồng thau, tiết diện cáp sử dụng 16 mm2 | Ống nối cáp điện; model: SL16, chất liệu đồng thau, tiết diện cáp sử dụng 16 mm2</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="n">
+        <v>66000</v>
+      </c>
+      <c r="L12" s="27" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="M12" s="64" t="n">
+        <v>32250000</v>
+      </c>
+      <c r="N12" s="65" t="n">
+        <v>90.71729957805907</v>
+      </c>
+      <c r="O12" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P12" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="24" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="R12" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" s="68" t="inlineStr">
+        <is>
+          <t>🟢 Trong hạn 12 tháng (8 tháng)</t>
+        </is>
+      </c>
+      <c r="U12" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 66,000 đ (giảm trừ 645,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Imatek/ Trung Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>770000</v>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm - Hãng: Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>Khóa cáp 4</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>1852</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>101860</v>
+      </c>
+      <c r="M13" s="64" t="n">
+        <v>668140</v>
+      </c>
+      <c r="N13" s="65" t="n">
+        <v>86.77142857142857</v>
+      </c>
+      <c r="O13" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P13" s="26" t="inlineStr">
+        <is>
+          <t>IB2600528351</t>
+        </is>
+      </c>
+      <c r="Q13" s="24" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="R13" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S13" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="68" t="inlineStr">
+        <is>
+          <t>🟢 Trong hạn 12 tháng (0 tháng)</t>
+        </is>
+      </c>
+      <c r="U13" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 1,852 đ (giảm trừ 12,148 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Kungho/ Trung Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>5.01.07.302.FRA.00.000</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>158000</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>316000</v>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302 - Hãng: SKF/ Pháp</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn  6302 
+Các thông số cơ bản:
+- Tải trọng động: 11.9 kN;
+- Tải trọng tĩnh: 5.4 kN;
+- Vận tốc tham khảo: 38000 v/ph;
+- Vận tốc giới hạn: 24000 v/ph; 
+Nhà sản xuất/XX: SKF/China, Eu-G7</t>
+        </is>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>40560</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <v>81120</v>
+      </c>
+      <c r="M14" s="64" t="n">
+        <v>234880</v>
+      </c>
+      <c r="N14" s="65" t="n">
+        <v>74.32911392405063</v>
+      </c>
+      <c r="O14" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P14" s="26" t="inlineStr">
+        <is>
+          <t>IB2300309906</t>
+        </is>
+      </c>
+      <c r="Q14" s="24" t="inlineStr">
+        <is>
+          <t>27/12/2023</t>
+        </is>
+      </c>
+      <c r="R14" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S14" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="T14" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (33 tháng - 2.8 năm)</t>
+        </is>
+      </c>
+      <c r="U14" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 40,560 đ (giảm trừ 117,440 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - SKF/ Pháp).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6208</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Vòng</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>444000</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1776000</v>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6208 - Hãng: SKF/ Pháp</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302 | Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>85000</v>
+      </c>
+      <c r="L15" s="27" t="n">
+        <v>340000</v>
+      </c>
+      <c r="M15" s="64" t="n">
+        <v>1436000</v>
+      </c>
+      <c r="N15" s="65" t="n">
+        <v>80.85585585585585</v>
+      </c>
+      <c r="O15" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P15" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho Bạc đạn (HĐ:223) theo hóa đơn số 0000792 ngày 31.12.2020 (phiếu sai)</t>
+        </is>
+      </c>
+      <c r="Q15" s="24" t="inlineStr">
+        <is>
+          <t>19/01/2021</t>
+        </is>
+      </c>
+      <c r="R15" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S15" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="T15" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (68 tháng - 5.7 năm)</t>
+        </is>
+      </c>
+      <c r="U15" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 85,000 đ (giảm trừ 359,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - SKF/ Pháp).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Keo phủ chống mài mòn Kalpoxy-150</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Cặp</t>
+        </is>
+      </c>
+      <c r="E16" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>16320000</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>326400000</v>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>Wear Resistant Mortar (Keo chống mài mòn)
+Keo phủ chống mài mòn Kalpoxy-150/Kalenborn 
+(01 cặp bao gồm hardener + Resin) - Hãng: Kalenborn/ Đức</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>Keo phủ chống mài mòn</t>
+        </is>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>1596000</v>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>31920000</v>
+      </c>
+      <c r="M16" s="64" t="n">
+        <v>294480000</v>
+      </c>
+      <c r="N16" s="65" t="n">
+        <v>90.22058823529412</v>
+      </c>
+      <c r="O16" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P16" s="26" t="inlineStr">
+        <is>
+          <t>IB2500075655</t>
+        </is>
+      </c>
+      <c r="Q16" s="24" t="inlineStr">
+        <is>
+          <t>11/05/2025</t>
+        </is>
+      </c>
+      <c r="R16" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S16" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="T16" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (16 tháng - 1.3 năm)</t>
+        </is>
+      </c>
+      <c r="U16" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 1,596,000 đ (giảm trừ 14,724,000 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Kalenborn/ Đức).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>3.70.75.349.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Cao su non, KT: B500x6x2800mm</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Cuộn</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>124000000</v>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>Cao su non, KT: B500x6x2800mm - Hãng: Rema Tiptop/ Đức</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="inlineStr">
+        <is>
+          <t>Cao su non; KT B500x6x2800mm; Mã 538 0048
+NSX: Rema TipTop</t>
+        </is>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>4881000</v>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>97620000</v>
+      </c>
+      <c r="M17" s="64" t="n">
+        <v>26380000</v>
+      </c>
+      <c r="N17" s="65" t="n">
+        <v>21.2741935483871</v>
+      </c>
+      <c r="O17" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P17" s="26" t="inlineStr">
+        <is>
+          <t>IB2300253768</t>
+        </is>
+      </c>
+      <c r="Q17" s="24" t="inlineStr">
+        <is>
+          <t>30/11/2023</t>
+        </is>
+      </c>
+      <c r="R17" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S17" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="T17" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (34 tháng - 2.8 năm)</t>
+        </is>
+      </c>
+      <c r="U17" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 4,881,000 đ (giảm trừ 1,319,000 đ/đơn vị) căn cứ theo Cơ sở 4: Mua Sắm Công e-GP, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Rema Tiptop/ Đức).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Bản quyền Windows 11 Pro</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="E18" s="63" t="n">
+        <v>123</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>651900000</v>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>Windows GGWA - Windows 11 Pro - Legalization Get Genuine - Hãng: Microsoft/ USA</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="inlineStr">
+        <is>
+          <t>Phần mềm Bản quyền Windows 11 Pro, Thời hạn bản quyền: vĩnh viễn | Đơn vị: Công ty Nhiệt điện Duyên Hải</t>
+        </is>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>553500000</v>
+      </c>
+      <c r="M18" s="64" t="n">
+        <v>98400000</v>
+      </c>
+      <c r="N18" s="65" t="n">
+        <v>15.09433962264151</v>
+      </c>
+      <c r="O18" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P18" s="26" t="inlineStr">
+        <is>
+          <t>134.23/DTG</t>
+        </is>
+      </c>
+      <c r="Q18" s="24" t="inlineStr">
+        <is>
+          <t>21/12/2023</t>
+        </is>
+      </c>
+      <c r="R18" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S18" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="T18" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (33 tháng - 2.8 năm)</t>
+        </is>
+      </c>
+      <c r="U18" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 4,500,000 đ (giảm trừ 800,000 đ/đơn vị) căn cứ theo Cơ sở 3: EVN IMIS, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (WINDOWS 11 - Microsoft/ USA). LÝ DO KỸ THUẬT KHÔNG ÁP DỤ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="E19" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>770000000</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>1540000000</v>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>Bơm (SP-Circulation pump):
+TP400 PP, P4-400V/50
+Động cơ bơm: type: FCA 112 MC-2/PHE, Công Suất : 5,5kW
+Điện áp: 400Vac
+Tần số: 50Hz
+Dòng định mức: 10.11A,
+Tốc độ quay: 2900 rpm
+Trọng lượng: 34kg
+Poles: 2P, Insulation class: F
+Degress of protection: IP55,
+PF: 0,88, Connection: Sao /Tam giác (400/690 YV), Eff: 0,87 - 0,89
+Standard Specification :
+IEC60034-1 - Hãng: Grundfos/ Eu</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá cạnh tranh</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>Báo giá cạnh tranh nộp kèm đợt thẩm định 2026</t>
+        </is>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="L19" s="27" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="M19" s="64" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="N19" s="65" t="n">
+        <v>2.597402597402597</v>
+      </c>
+      <c r="O19" s="66" t="inlineStr">
+        <is>
+          <t>✅ Báo giá cạnh tranh đáp ứng 100% hồ sơ yêu cầu kỹ thuật</t>
+        </is>
+      </c>
+      <c r="P19" s="26" t="inlineStr">
+        <is>
+          <t>Báo giá NCC chào cạnh tranh</t>
+        </is>
+      </c>
+      <c r="Q19" s="24" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="R19" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S19" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="68" t="inlineStr">
+        <is>
+          <t>🟢 Trong hạn 12 tháng (0 tháng)</t>
+        </is>
+      </c>
+      <c r="U19" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 750,000,000 đ (giảm trừ 20,000,000 đ/đơn vị) căn cứ theo Cơ sở 1: Báo giá cạnh tranh, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (TP400 - Grundfos/ Eu). LÝ DO KỸ THUẬT KHÔ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>5.33.85.051.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Phanh đuôi động cơ, model: BFK458-18E</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>63063000</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>126126000</v>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>Model: BFK458-18E
+Size: 18
+Đường kính phủ bì: 218,6mm
+Lỗ lắp bulong: 6xM8
+Đường kính vòng chia bulong: 196mm
+Điện áp: 205VDC
+Nhà sản xuất: INTORQ - Hãng: Intorq/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
+        </is>
+      </c>
+      <c r="J20" s="26" t="inlineStr">
+        <is>
+          <t>Phanh xe lớn Loại BFK458-16E | Đơn vị: Công ty Cổ phần Thủy điện Sông Ba Hạ</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="L20" s="27" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="M20" s="64" t="n">
+        <v>65366000</v>
+      </c>
+      <c r="N20" s="65" t="n">
+        <v>51.82595182595182</v>
+      </c>
+      <c r="O20" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P20" s="26" t="inlineStr">
+        <is>
+          <t>30/HĐ-SBH</t>
+        </is>
+      </c>
+      <c r="Q20" s="24" t="inlineStr">
+        <is>
+          <t>17/05/2024</t>
+        </is>
+      </c>
+      <c r="R20" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S20" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="T20" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (28 tháng - 2.3 năm)</t>
+        </is>
+      </c>
+      <c r="U20" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 30,380,000 đ (giảm trừ 32,683,000 đ/đơn vị) căn cứ theo Cơ sở 3: EVN IMIS, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (BFK458-18E - Intorq/ Trung Quốc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>1.31.23.425.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương - Hãng: Shell/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="inlineStr">
+        <is>
+          <t>Dầu hộp số Shell Omala S4 WE 220 | Đơn vị: EVN - Công ty Nhiệt điện Thái Bình</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="n">
+        <v>347000</v>
+      </c>
+      <c r="L21" s="27" t="n">
+        <v>6940000</v>
+      </c>
+      <c r="M21" s="64" t="n">
+        <v>4260000</v>
+      </c>
+      <c r="N21" s="65" t="n">
+        <v>38.03571428571428</v>
+      </c>
+      <c r="O21" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P21" s="26" t="inlineStr">
+        <is>
+          <t>72/HĐ-HH04-2023</t>
+        </is>
+      </c>
+      <c r="Q21" s="24" t="inlineStr">
+        <is>
+          <t>01/08/2023</t>
+        </is>
+      </c>
+      <c r="R21" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S21" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="T21" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (37 tháng - 3.1 năm)</t>
+        </is>
+      </c>
+      <c r="U21" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá đề nghị 347,000 đ (giảm trừ 213,000 đ/đơn vị) căn cứ theo Cơ sở 3: EVN IMIS, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (WE 220 - Shell/ Trung Quốc). LÝ DO KỸ THUẬT KHÔNG ÁP DỤNG </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>5.30.10.355.VIE.99.000</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD - Hãng: Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t>Gầu múc ĐPĐ, thể tích 0.75m3, vật liệu: SMS570(JIS)+A709(ASTM) | Gầu múc ĐPĐ, thể tích 0.75m3, vật liệu: SMS570(JIS)+A709(ASTM)</t>
+        </is>
+      </c>
+      <c r="K22" s="27" t="n">
+        <v>137382000</v>
+      </c>
+      <c r="L22" s="27" t="n">
+        <v>274764000</v>
+      </c>
+      <c r="M22" s="64" t="n">
+        <v>255236000</v>
+      </c>
+      <c r="N22" s="65" t="n">
+        <v>48.15773584905661</v>
+      </c>
+      <c r="O22" s="66" t="inlineStr">
+        <is>
+          <t>✅ Khớp đúng Model &amp; Thông số kỹ thuật yêu cầu</t>
+        </is>
+      </c>
+      <c r="P22" s="26" t="inlineStr">
+        <is>
+          <t>Nhập kho vật tư (HĐ: 63/2024) theo hóa đơn số 37 ngày 22.10.2024</t>
+        </is>
+      </c>
+      <c r="Q22" s="24" t="inlineStr">
+        <is>
+          <t>04/11/2024</t>
+        </is>
+      </c>
+      <c r="R22" s="24" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="S22" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="T22" s="67" t="inlineStr">
+        <is>
+          <t>🟡 Quá 12 tháng (22 tháng - 1.8 năm)</t>
+        </is>
+      </c>
+      <c r="U22" s="26" t="inlineStr">
+        <is>
+          <t>Đơn giá đề nghị 137,382,000 đ (giảm trừ 127,618,000 đ/đơn vị) căn cứ theo Cơ sở 2: CSDL ERP Vĩnh Tân 4, bảo đảm trùng khớp chính xác thông số kỹ thuật và Model (Theo thiết kế - Việt Nam).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG (18 MỤC TIẾT GIẢM):</t>
+        </is>
+      </c>
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="50" t="n"/>
+      <c r="E23" s="50" t="n"/>
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="51" t="n">
+        <v>3684646000</v>
+      </c>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="50" t="n"/>
+      <c r="L23" s="51" t="n">
+        <v>2617235526</v>
+      </c>
+      <c r="M23" s="52" t="n">
+        <v>1067410474</v>
+      </c>
+      <c r="N23" s="69" t="n">
+        <v>28.9691458555313</v>
+      </c>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="50" t="n"/>
+      <c r="R23" s="50" t="n"/>
+      <c r="S23" s="50" t="n"/>
+      <c r="T23" s="50" t="n"/>
+      <c r="U23" s="50" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>